--- a/data/trans_dic/P38C-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P38C-Edad-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de glucosal por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de glucosal por prescripción médica (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,32; 61,46</t>
+          <t>51,28; 60,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39,57; 57,32</t>
+          <t>40,43; 57,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,46; 69,78</t>
+          <t>60,5; 69,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,52; 67,73</t>
+          <t>53,0; 67,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,43; 64,61</t>
+          <t>57,27; 64,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,87; 59,49</t>
+          <t>47,49; 59,57</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,64; 72,27</t>
+          <t>64,72; 72,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,35; 70,83</t>
+          <t>59,54; 70,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78,8; 85,21</t>
+          <t>79,24; 85,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,17; 78,21</t>
+          <t>39,99; 77,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,51; 77,94</t>
+          <t>72,52; 77,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,01; 72,58</t>
+          <t>48,14; 72,38</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,01; 84,29</t>
+          <t>77,8; 84,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72,9; 80,65</t>
+          <t>73,3; 80,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,45; 87,85</t>
+          <t>82,47; 88,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81,43; 86,85</t>
+          <t>81,96; 86,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,06; 85,22</t>
+          <t>81,22; 85,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,58; 83,14</t>
+          <t>78,59; 83,04</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,38; 89,88</t>
+          <t>84,24; 89,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,34; 87,23</t>
+          <t>26,35; 87,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,99; 92,49</t>
+          <t>87,81; 92,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,96; 92,88</t>
+          <t>88,2; 92,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,89; 90,46</t>
+          <t>86,82; 90,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,55; 89,24</t>
+          <t>48,42; 89,42</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,39; 94,66</t>
+          <t>89,16; 94,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89,44; 93,84</t>
+          <t>89,03; 93,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,48; 95,15</t>
+          <t>90,57; 95,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91,67; 95,13</t>
+          <t>91,6; 95,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,71; 94,32</t>
+          <t>90,58; 94,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,35; 93,91</t>
+          <t>91,32; 94,1</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>94,57; 98,48</t>
+          <t>94,8; 98,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92,99; 96,66</t>
+          <t>93,03; 96,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95,87; 98,96</t>
+          <t>95,86; 98,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96,65; 99,3</t>
+          <t>96,51; 99,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>96,1; 98,34</t>
+          <t>96,14; 98,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95,64; 98,51</t>
+          <t>95,58; 98,45</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,08; 98,86</t>
+          <t>95,06; 98,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>97,07; 99,33</t>
+          <t>96,57; 99,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95,7; 99,38</t>
+          <t>95,28; 99,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94,86; 97,81</t>
+          <t>95,03; 97,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,43; 98,94</t>
+          <t>96,29; 98,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,15; 98,18</t>
+          <t>96,18; 98,2</t>
         </is>
       </c>
     </row>
@@ -1197,27 +1197,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57,23; 80,95</t>
+          <t>58,16; 81,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,35; 88,57</t>
+          <t>86,35; 88,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80,73; 88,75</t>
+          <t>80,58; 88,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>83,65; 85,33</t>
+          <t>83,65; 85,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,67; 84,5</t>
+          <t>72,13; 84,41</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de glucosal por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de glucosal por prescripción médica (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>206825; 247716</t>
+          <t>206683; 244961</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>158285; 229255</t>
+          <t>161718; 231920</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>237499; 274110</t>
+          <t>237667; 274293</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164050; 207579</t>
+          <t>162446; 207769</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>457072; 514226</t>
+          <t>455804; 510297</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>338182; 420300</t>
+          <t>335512; 420877</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>380352; 425260</t>
+          <t>380816; 424985</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>251362; 300015</t>
+          <t>252182; 300634</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>443272; 479337</t>
+          <t>445776; 480714</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>205472; 400025</t>
+          <t>204549; 398673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>834527; 897060</t>
+          <t>834712; 892133</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>467648; 678632</t>
+          <t>450128; 676766</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>515160; 556634</t>
+          <t>513773; 555011</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>389892; 431368</t>
+          <t>392035; 432009</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>538413; 573660</t>
+          <t>538552; 574746</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>441585; 470984</t>
+          <t>444456; 471298</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1064711; 1119332</t>
+          <t>1066816; 1121969</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>846380; 895569</t>
+          <t>846508; 894475</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>538095; 573218</t>
+          <t>537213; 573904</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>242709; 774418</t>
+          <t>233900; 775547</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>569312; 598417</t>
+          <t>568166; 598174</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>626574; 661608</t>
+          <t>628311; 662097</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1116275; 1162201</t>
+          <t>1115452; 1161532</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>712801; 1428006</t>
+          <t>774789; 1430815</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>427208; 452414</t>
+          <t>426123; 451366</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>501960; 526673</t>
+          <t>499690; 524931</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>448459; 471608</t>
+          <t>448920; 472516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>502262; 521214</t>
+          <t>501885; 521840</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>883168; 918227</t>
+          <t>881819; 917082</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1013214; 1041624</t>
+          <t>1012842; 1043699</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>316162; 329239</t>
+          <t>316929; 329460</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>342373; 355872</t>
+          <t>342510; 355735</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>362150; 373832</t>
+          <t>362135; 373828</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>587988; 604130</t>
+          <t>587165; 604279</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>684332; 700268</t>
+          <t>684630; 701512</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>933982; 962022</t>
+          <t>933337; 961379</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>243568; 253236</t>
+          <t>243508; 253010</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>274483; 280854</t>
+          <t>273046; 280690</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>381792; 396475</t>
+          <t>380136; 396480</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>403400; 415931</t>
+          <t>404138; 415981</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>631734; 648149</t>
+          <t>630824; 647373</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>680737; 695103</t>
+          <t>680957; 695269</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2689338; 2782281</t>
+          <t>2689455; 2781973</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1979099; 2799393</t>
+          <t>2011517; 2802762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3046246; 3124396</t>
+          <t>3046105; 3120388</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2949914; 3243177</t>
+          <t>2944456; 3237367</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5759974; 5875968</t>
+          <t>5760286; 5881794</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5026322; 6009920</t>
+          <t>5130186; 6003651</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38C-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P38C-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,28; 60,78</t>
+          <t>50,86; 61,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40,43; 57,98</t>
+          <t>37,24; 53,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60,5; 69,83</t>
+          <t>61,21; 70,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,0; 67,79</t>
+          <t>51,6; 65,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>57,27; 64,12</t>
+          <t>57,61; 64,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,49; 59,57</t>
+          <t>46,32; 57,1</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,72; 72,22</t>
+          <t>64,13; 72,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,54; 70,98</t>
+          <t>58,26; 70,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,24; 85,45</t>
+          <t>78,92; 85,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,99; 77,94</t>
+          <t>71,06; 79,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,52; 77,51</t>
+          <t>72,43; 77,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,14; 72,38</t>
+          <t>66,41; 73,61</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>77,8; 84,04</t>
+          <t>77,77; 84,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73,3; 80,77</t>
+          <t>71,51; 78,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,47; 88,01</t>
+          <t>82,28; 87,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>81,96; 86,91</t>
+          <t>81,44; 86,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>81,22; 85,42</t>
+          <t>81,02; 85,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,59; 83,04</t>
+          <t>77,45; 82,0</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,24; 89,99</t>
+          <t>83,98; 89,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,35; 87,36</t>
+          <t>83,4; 88,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,81; 92,45</t>
+          <t>87,72; 92,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,2; 92,95</t>
+          <t>88,84; 92,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,82; 90,41</t>
+          <t>86,92; 90,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,42; 89,42</t>
+          <t>86,9; 90,25</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>89,16; 94,44</t>
+          <t>89,34; 94,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>89,03; 93,53</t>
+          <t>88,55; 93,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,57; 95,33</t>
+          <t>89,98; 95,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>91,6; 95,24</t>
+          <t>92,44; 95,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,58; 94,2</t>
+          <t>90,86; 94,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>91,32; 94,1</t>
+          <t>91,2; 93,87</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>94,8; 98,54</t>
+          <t>94,88; 98,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93,03; 96,62</t>
+          <t>92,8; 96,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95,86; 98,96</t>
+          <t>96,0; 98,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96,51; 99,33</t>
+          <t>95,31; 97,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>96,14; 98,51</t>
+          <t>96,21; 98,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95,58; 98,45</t>
+          <t>94,55; 96,92</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,06; 98,77</t>
+          <t>94,74; 98,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96,57; 99,27</t>
+          <t>96,3; 99,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>95,28; 99,38</t>
+          <t>95,88; 99,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95,03; 97,82</t>
+          <t>94,75; 97,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,29; 98,82</t>
+          <t>96,4; 98,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,18; 98,2</t>
+          <t>95,91; 97,99</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>80,09; 82,85</t>
+          <t>79,87; 82,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>58,16; 81,04</t>
+          <t>77,73; 81,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,35; 88,45</t>
+          <t>86,21; 88,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80,58; 88,59</t>
+          <t>85,37; 87,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>83,65; 85,42</t>
+          <t>83,63; 85,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>72,13; 84,41</t>
+          <t>81,94; 84,0</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>194211</t>
+          <t>181983</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186977</t>
+          <t>210049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>381188</t>
+          <t>392031</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>206683; 244961</t>
+          <t>204998; 245970</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>161718; 231920</t>
+          <t>151864; 217655</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>237667; 274293</t>
+          <t>240444; 276021</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>162446; 207769</t>
+          <t>182575; 232604</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>455804; 510297</t>
+          <t>458514; 511797</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>335512; 420877</t>
+          <t>352810; 434875</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>277244</t>
+          <t>306008</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>339586</t>
+          <t>377558</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>616830</t>
+          <t>683566</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>380816; 424985</t>
+          <t>377388; 427398</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>252182; 300634</t>
+          <t>277817; 334445</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>445776; 480714</t>
+          <t>443953; 479559</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>204549; 398673</t>
+          <t>356086; 397106</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>834712; 892133</t>
+          <t>833681; 892184</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>450128; 676766</t>
+          <t>649472; 719873</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>413198</t>
+          <t>464843</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>458134</t>
+          <t>523291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>871332</t>
+          <t>988134</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>513773; 555011</t>
+          <t>513630; 555025</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>392035; 432009</t>
+          <t>442924; 487350</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>538552; 574746</t>
+          <t>537292; 574112</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>444456; 471298</t>
+          <t>505979; 540176</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1066816; 1121969</t>
+          <t>1064176; 1119290</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>846508; 894475</t>
+          <t>960923; 1017337</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>553821</t>
+          <t>605399</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>648112</t>
+          <t>666722</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1201933</t>
+          <t>1272121</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>537213; 573904</t>
+          <t>535582; 572606</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>233900; 775547</t>
+          <t>584298; 622034</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>568166; 598174</t>
+          <t>567591; 597523</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>628311; 662097</t>
+          <t>653651; 679015</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1115452; 1161532</t>
+          <t>1116662; 1164134</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>774789; 1430815</t>
+          <t>1248206; 1296358</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>515538</t>
+          <t>553972</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>513578</t>
+          <t>572694</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1029116</t>
+          <t>1126667</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>426123; 451366</t>
+          <t>426995; 451459</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>499690; 524931</t>
+          <t>539576; 567351</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>448920; 472516</t>
+          <t>445997; 471617</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>501885; 521840</t>
+          <t>562835; 580853</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>881819; 917082</t>
+          <t>884622; 917820</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1012842; 1043699</t>
+          <t>1111047; 1143485</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>349956</t>
+          <t>385856</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>596519</t>
+          <t>425253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>946475</t>
+          <t>811109</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>316929; 329460</t>
+          <t>317217; 330061</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>342510; 355735</t>
+          <t>377777; 392569</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>362135; 373828</t>
+          <t>362666; 373894</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>587165; 604279</t>
+          <t>418574; 429659</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>684630; 701512</t>
+          <t>685097; 701053</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>933337; 961379</t>
+          <t>800147; 820189</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>278288</t>
+          <t>304329</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>410731</t>
+          <t>447385</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>689019</t>
+          <t>751714</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>243508; 253010</t>
+          <t>242686; 253042</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>273046; 280690</t>
+          <t>298706; 307663</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>380136; 396480</t>
+          <t>382538; 396462</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>404138; 415981</t>
+          <t>439646; 453329</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>630824; 647373</t>
+          <t>631547; 647871</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>680957; 695269</t>
+          <t>742563; 758674</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2582257</t>
+          <t>2802391</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3153638</t>
+          <t>3222951</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5735894</t>
+          <t>6025342</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2689455; 2781973</t>
+          <t>2682118; 2780488</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2011517; 2802762</t>
+          <t>2744836; 2860933</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3046105; 3120388</t>
+          <t>3041339; 3123681</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2944456; 3237367</t>
+          <t>3179365; 3264943</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5760286; 5881794</t>
+          <t>5758371; 5881600</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5130186; 6003651</t>
+          <t>5945412; 6094685</t>
         </is>
       </c>
     </row>
